--- a/artfynd/A 3134-2024 artfynd.xlsx
+++ b/artfynd/A 3134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,1995 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114817551</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>464877</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7030452</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skalad granraka/ringhack.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114818419</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90204</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ingridholmen (Ingridholmen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>464522</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7030385</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114818281</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78453</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>464721</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7030502</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om i området.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114818703</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kavelbroviken (Näldsjön), Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465006</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7030687</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Ringbarkade granar. Ffa klenare senvuxet.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114818373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90258</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>464685</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7030475</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114818426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90204</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ingridholmen (Ingridholmen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>464523</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7030385</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114818356</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>464669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7030499</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack och skalade granar i området.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114818261</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464752</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7030475</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack/skalad gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114818409</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90258</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464584</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7030400</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114817525</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464906</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7030472</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack lågt i äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114818645</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90258</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>464924</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7030522</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114818551</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>464720</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7030516</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skalad gran/ringhack.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114818684</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78453</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>465033</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7030651</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114817680</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90933</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>67</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>464872</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7030449</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På lutande klen, senvuxen gran i sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114818186</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78453</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>464869</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7030450</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114818219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78453</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>464829</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7030464</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På torraka med spillkråkehack.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114818393</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>464641</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7030463</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3134-2024 artfynd.xlsx
+++ b/artfynd/A 3134-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3134-2024 artfynd.xlsx
+++ b/artfynd/A 3134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80914003</v>
+        <v>114817680</v>
       </c>
       <c r="B2" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>avk2019MITT399, Jmt</t>
+          <t>Åbergsnäset, Åbergsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465028.0649933565</v>
+        <v>464872</v>
       </c>
       <c r="R2" t="n">
-        <v>7030716.864683645</v>
+        <v>7030449</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,30 +741,29 @@
           <t>Näskott</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Innerslänt</t>
+          <t>På lutande klen, senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,76 +772,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Andersson, Magnus Sjölund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114818281</v>
+        <v>114818419</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Ingridholmen, Ingridholmen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464721</v>
+        <v>464522</v>
       </c>
       <c r="R3" t="n">
-        <v>7030502</v>
+        <v>7030385</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gott om i området.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,12 +902,7 @@
         <v>114818426</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,7 +931,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingridholmen (Ingridholmen), Jmt</t>
+          <t>Ingridholmen, Ingridholmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1032,51 +1007,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114818645</v>
+        <v>114818186</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+          <t>Åbergsnäset, Åbergsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464924</v>
+        <v>464869</v>
       </c>
       <c r="R5" t="n">
-        <v>7030522</v>
+        <v>7030451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,12 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt på högstubbe.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,51 +1115,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114818551</v>
+        <v>114818219</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+          <t>Åbergsnäset, Åbergsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464720</v>
+        <v>464829</v>
       </c>
       <c r="R6" t="n">
-        <v>7030516</v>
+        <v>7030464</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1226,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Skalad gran/ringhack.</t>
+          <t>På torraka med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,19 +1228,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114818186</v>
+        <v>114818281</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1305,17 +1260,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Åbergsnäset, Åbergsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464869</v>
+        <v>464721</v>
       </c>
       <c r="R7" t="n">
-        <v>7030451</v>
+        <v>7030502</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gott om i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,54 +1341,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114818703</v>
+        <v>114818684</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kavelbroviken (Näldsjön), Jmt</t>
+          <t>Kavelbroviken, Kavelbroviken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465006</v>
+        <v>465033</v>
       </c>
       <c r="R8" t="n">
-        <v>7030687</v>
+        <v>7030651</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,11 +1423,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack. Ringbarkade granar. Ffa klenare senvuxet.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,51 +1449,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114818409</v>
+        <v>114817525</v>
       </c>
       <c r="B9" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Kavelbroviken, Kavelbroviken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464584</v>
+        <v>464907</v>
       </c>
       <c r="R9" t="n">
-        <v>7030400</v>
+        <v>7030471</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1575,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,7 +1535,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack lågt i äldre gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,32 +1567,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114818261</v>
+        <v>114818393</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1647,16 +1597,21 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+          <t>Åbergsnäset, Nordannälden, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464752</v>
+        <v>464641</v>
       </c>
       <c r="R10" t="n">
-        <v>7030475</v>
+        <v>7030463</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1688,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,12 +1653,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack/skalad gran.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,15 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114818356</v>
+        <v>114817551</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,19 +1710,24 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+          <t>Åbergsnäset, Åbergsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464670</v>
+        <v>464877</v>
       </c>
       <c r="R11" t="n">
-        <v>7030499</v>
+        <v>7030452</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1766,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack och skalade granar i området.</t>
+          <t>Skalad granraka/ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,15 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114818373</v>
+        <v>114818261</v>
       </c>
       <c r="B12" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,38 +1809,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Åbergsnäset, Nordannälden, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464685</v>
+        <v>464752</v>
       </c>
       <c r="R12" t="n">
         <v>7030475</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1879,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack/skalad gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,56 +1911,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114817680</v>
+        <v>114818356</v>
       </c>
       <c r="B13" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Åbergsnäset, Nordannälden, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464872</v>
+        <v>464670</v>
       </c>
       <c r="R13" t="n">
-        <v>7030449</v>
+        <v>7030499</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,12 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På lutande klen, senvuxen gran i sumpskog.</t>
+          <t>Äldre och färska ringhack och skalade granar i området.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,7 +2006,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2082,54 +2024,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114818419</v>
+        <v>114818551</v>
       </c>
       <c r="B14" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingridholmen (Ingridholmen), Jmt</t>
+          <t>Åbergsnäset, Nordannälden, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464522</v>
+        <v>464720</v>
       </c>
       <c r="R14" t="n">
-        <v>7030385</v>
+        <v>7030516</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2105,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skalad gran/ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,15 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114817525</v>
+        <v>114818703</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,16 +2148,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2230,21 +2167,16 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+          <t>Kavelbroviken, Näldsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464907</v>
+        <v>465006</v>
       </c>
       <c r="R15" t="n">
-        <v>7030471</v>
+        <v>7030687</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2276,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2218,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack lågt i äldre gran.</t>
+          <t>Ringhack. Ringbarkade granar. Ffa klenare senvuxet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,15 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114818219</v>
+        <v>115215771</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,38 +2261,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Brattmelarna Nordanälden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464829</v>
+        <v>464671</v>
       </c>
       <c r="R16" t="n">
-        <v>7030464</v>
+        <v>7030465</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2389,34 +2315,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På torraka med spillkråkehack.</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2424,27 +2340,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114817551</v>
+        <v>115215772</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,25 +2381,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Åbergsnäset), Jmt</t>
+          <t>Brattmelarna Nordanälden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464877</v>
+        <v>464729</v>
       </c>
       <c r="R17" t="n">
-        <v>7030452</v>
+        <v>7030478</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2512,27 +2417,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Skalad granraka/ringhack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,27 +2442,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114818684</v>
+        <v>115215773</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,35 +2465,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kavelbroviken (Kavelbroviken), Jmt</t>
+          <t>Brattmelarna Nordanälden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465033</v>
+        <v>464507</v>
       </c>
       <c r="R18" t="n">
-        <v>7030651</v>
+        <v>7030380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,22 +2519,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,27 +2544,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114818393</v>
+        <v>115215774</v>
       </c>
       <c r="B19" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,16 +2567,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2706,25 +2585,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åbergsnäset (Nordannälden, Näskott), Jmt</t>
+          <t>Brattmelarna Nordanälden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464641</v>
+        <v>464400</v>
       </c>
       <c r="R19" t="n">
-        <v>7030463</v>
+        <v>7030336</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2748,22 +2621,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2778,27 +2646,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115215772</v>
+        <v>115215775</v>
       </c>
       <c r="B20" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464729</v>
+        <v>464509</v>
       </c>
       <c r="R20" t="n">
-        <v>7030478</v>
+        <v>7030384</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2897,15 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115215773</v>
+        <v>115215776</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464507</v>
+        <v>464523</v>
       </c>
       <c r="R21" t="n">
-        <v>7030380</v>
+        <v>7030373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3004,15 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115215775</v>
+        <v>80914003</v>
       </c>
       <c r="B22" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,37 +2873,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>222112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattmelarna Nordanälden, Jmt</t>
+          <t>avk2019MITT399, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464509</v>
+        <v>465028</v>
       </c>
       <c r="R22" t="n">
-        <v>7030384</v>
+        <v>7030717</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3072,19 +2929,20 @@
           <t>Näskott</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Innerslänt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,336 +2957,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>115215774</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Brattmelarna Nordanälden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>464400</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7030336</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Näskott</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>115215776</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Brattmelarna Nordanälden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>464523</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7030373</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Näskott</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>115215771</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Brattmelarna Nordanälden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>464671</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7030465</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Näskott</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Klas Andersson, Magnus Sjölund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3134-2024 artfynd.xlsx
+++ b/artfynd/A 3134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114817680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818281</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818684</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114817525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818393</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114817551</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818261</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2021,6 +2081,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2134,6 +2199,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114818703</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215771</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2451,6 +2531,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215772</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2553,6 +2638,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215773</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2655,6 +2745,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215774</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2757,6 +2852,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215775</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215776</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2970,8 +3075,36 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80914003</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>